--- a/docs/EV_Charging_Optimizer_Model.xlsx
+++ b/docs/EV_Charging_Optimizer_Model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bladz\Desktop\Laurea_Linux\Basics of Programing\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65213ADA-F1C1-47C1-B4E0-86BB8836DCBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC32755F-A399-495E-B973-3BA682786E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7802,6 +7802,187 @@
     </xdr:graphicFrame>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>14286</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>923924</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>102577</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="TextBox 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A1A5392-F3FC-5D2B-2B01-A70A4433AD81}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="5919786"/>
+          <a:ext cx="2425943" cy="1231291"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent3"/>
+        </a:lnRef>
+        <a:fillRef idx="3">
+          <a:schemeClr val="accent3"/>
+        </a:fillRef>
+        <a:effectRef idx="2">
+          <a:schemeClr val="accent3"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Trebuchet MS" panose="020B0603020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Israel Gacia</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-FI" sz="1400" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Trebuchet MS" panose="020B0603020202020204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>Basics of Programming ND00CC70-3002</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" sz="1400" b="1" i="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="Trebuchet MS" panose="020B0603020202020204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" defTabSz="914400" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
+            <a:defRPr/>
+          </a:pPr>
+          <a:r>
+            <a:rPr lang="en-FI" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Trebuchet MS" panose="020B0603020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>EV Charging Optimizer</a:t>
+          </a:r>
+          <a:br>
+            <a:rPr lang="en-FI" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Trebuchet MS" panose="020B0603020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+          </a:br>
+          <a:r>
+            <a:rPr lang="en-FI" sz="1400">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="85000"/>
+                  <a:lumOff val="15000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="Trebuchet MS" panose="020B0603020202020204" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>Final Assignment</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-FI" sz="1400" b="1" i="0">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="Trebuchet MS" panose="020B0603020202020204" pitchFamily="34" charset="0"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
